--- a/artfynd/A 5005-2022 artfynd.xlsx
+++ b/artfynd/A 5005-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5005-2022 artfynd.xlsx
+++ b/artfynd/A 5005-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114584979</v>
+        <v>114585253</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363364</v>
+        <v>363386</v>
       </c>
       <c r="R2" t="n">
-        <v>6333196</v>
+        <v>6333213</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114585253</v>
+        <v>114585074</v>
       </c>
       <c r="B3" t="n">
-        <v>90129</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1067</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363386</v>
+        <v>363404</v>
       </c>
       <c r="R3" t="n">
-        <v>6333213</v>
+        <v>6333346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114585215</v>
+        <v>114585114</v>
       </c>
       <c r="B4" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229504</v>
+        <v>2609</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363610</v>
+        <v>363400</v>
       </c>
       <c r="R4" t="n">
-        <v>6333413</v>
+        <v>6333346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt inom 1x1 m</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Lönnberg, Stefan Lindkvist</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1003,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114585074</v>
+        <v>114585099</v>
       </c>
       <c r="B5" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363404</v>
+        <v>363604</v>
       </c>
       <c r="R5" t="n">
-        <v>6333346</v>
+        <v>6333374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1038,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Ullared</t>
+          <t>Gällared</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1109,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114585114</v>
+        <v>114585032</v>
       </c>
       <c r="B6" t="n">
-        <v>96305</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2609</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363400</v>
+        <v>363357</v>
       </c>
       <c r="R6" t="n">
-        <v>6333346</v>
+        <v>6333190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114585302</v>
+        <v>114584976</v>
       </c>
       <c r="B7" t="n">
-        <v>43639</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363420</v>
+        <v>363485</v>
       </c>
       <c r="R7" t="n">
-        <v>6333246</v>
+        <v>6333472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1245,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,7 +1275,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Lindkvist</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1321,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114585291</v>
+        <v>114584977</v>
       </c>
       <c r="B8" t="n">
-        <v>43639</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363356</v>
+        <v>363618</v>
       </c>
       <c r="R8" t="n">
-        <v>6333203</v>
+        <v>6333391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1346,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Ullared</t>
+          <t>Gällared</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1397,6 +1357,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,16 +1395,11 @@
         <v>114584978</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1538,15 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114585032</v>
+        <v>114584979</v>
       </c>
       <c r="B10" t="n">
-        <v>94179</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,21 +1509,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363357</v>
+        <v>363364</v>
       </c>
       <c r="R10" t="n">
-        <v>6333190</v>
+        <v>6333196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1569,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,15 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114584989</v>
+        <v>114585291</v>
       </c>
       <c r="B11" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,38 +1615,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hömossen, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363545</v>
+        <v>363356</v>
       </c>
       <c r="R11" t="n">
-        <v>6333377</v>
+        <v>6333203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,12 +1669,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,7 +1694,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Lindkvist</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1754,37 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114585217</v>
+        <v>114585302</v>
       </c>
       <c r="B12" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229504</v>
+        <v>101735</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363600</v>
+        <v>363420</v>
       </c>
       <c r="R12" t="n">
-        <v>6333398</v>
+        <v>6333246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,11 +1778,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>spridda exemplar på stam, 2 x1 m</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1854,10 +1795,736 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
+          <t>Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>JMN0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114584989</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hömossen, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>363545</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6333377</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ullared</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>JMN0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114585212</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hömossen, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>363603</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6333372</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gällared</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
           <t>Elin Lönnberg, Stefan Lindkvist</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>JMN0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114585213</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hömossen, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>363612</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6333379</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gällared</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg, Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>JMN0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114585214</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hömossen, Hl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>363604</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6333373</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gällared</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>spritt över hela stammen</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg, Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>JMN0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114585215</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hömossen, Hl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>363610</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6333413</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ullared</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>rikligt inom 1x1 m</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg, Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>JMN0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114585216</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hömossen, Hl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>363616</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6333419</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ullared</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg, Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>JMN0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114585217</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hömossen, Hl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>363600</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6333398</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ullared</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>spridda exemplar på stam, 2 x1 m</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg, Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
         <is>
           <t>JMN0118</t>
         </is>

--- a/artfynd/A 5005-2022 artfynd.xlsx
+++ b/artfynd/A 5005-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585253</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585032</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114584976</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114584977</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114584978</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114584979</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585291</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585302</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114584989</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585212</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585213</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585214</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2322,6 +2402,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585215</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585216</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2529,8 +2619,33 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>